--- a/output/yearly_surface_area_iteration_54_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_54_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497641857168</v>
+        <v>10.84497619611139</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907224281717</v>
+        <v>37.78907146765939</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.21446296788231</v>
+        <v>5.991606239018283</v>
       </c>
       <c r="C2" t="n">
-        <v>8.455792976677778</v>
+        <v>6.665085164131596</v>
       </c>
       <c r="D2" t="n">
-        <v>31.7801549341735</v>
+        <v>26.30494798758903</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.92947839621025</v>
+        <v>18.20160243673586</v>
       </c>
       <c r="C3" t="n">
-        <v>21.13211933391259</v>
+        <v>45.44510122958485</v>
       </c>
       <c r="D3" t="n">
-        <v>80.54258165640833</v>
+        <v>60.84381397069607</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.37299167881833</v>
+        <v>31.61325782445154</v>
       </c>
       <c r="C4" t="n">
-        <v>41.93829843001524</v>
+        <v>79.43517024601793</v>
       </c>
       <c r="D4" t="n">
-        <v>100.5191839424224</v>
+        <v>75.79779500178348</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.8784528777852</v>
+        <v>40.57072387799944</v>
       </c>
       <c r="C5" t="n">
-        <v>83.52218593879741</v>
+        <v>108.3849465488479</v>
       </c>
       <c r="D5" t="n">
-        <v>69.53228115328035</v>
+        <v>56.05779391249288</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.67304662341937</v>
+        <v>39.40637110076273</v>
       </c>
       <c r="C6" t="n">
-        <v>107.8744377426395</v>
+        <v>122.9688086954342</v>
       </c>
       <c r="D6" t="n">
-        <v>48.1409804254466</v>
+        <v>41.13719230334986</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.39865598784899</v>
+        <v>28.14670668075605</v>
       </c>
       <c r="C7" t="n">
-        <v>90.48866764813275</v>
+        <v>124.6240353247943</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>37.84833749412304</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.27385085622263</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="C8" t="n">
-        <v>57.57950285407543</v>
+        <v>81.52923809917637</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.431249284071605</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>34.83437204208531</v>
+        <v>42.3781214015178</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -926,7 +926,7 @@
         <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.699849194051904</v>
+        <v>7.693284055936877</v>
       </c>
       <c r="C21" t="n">
-        <v>94.32315262713581</v>
+        <v>94.24272968522673</v>
       </c>
       <c r="D21" t="n">
-        <v>8.662330343308392</v>
+        <v>8.654944562928987</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.059166904162065</v>
+        <v>5.846307578789756</v>
       </c>
       <c r="C2" t="n">
-        <v>5.42317431825938</v>
+        <v>6.253732876052181</v>
       </c>
       <c r="D2" t="n">
-        <v>27.53605960871454</v>
+        <v>27.35443628342888</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.36635612460008</v>
+        <v>19.21280257211008</v>
       </c>
       <c r="C3" t="n">
-        <v>27.18950266911541</v>
+        <v>35.14165907351457</v>
       </c>
       <c r="D3" t="n">
-        <v>85.78511439708629</v>
+        <v>66.36614480708438</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.77314383152353</v>
+        <v>32.68532631748906</v>
       </c>
       <c r="C4" t="n">
-        <v>47.03062377194345</v>
+        <v>96.35853717182444</v>
       </c>
       <c r="D4" t="n">
-        <v>114.264633549582</v>
+        <v>86.93964969728053</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.42532740677969</v>
+        <v>43.56505437595222</v>
       </c>
       <c r="C5" t="n">
-        <v>80.40513697781378</v>
+        <v>125.5164439879547</v>
       </c>
       <c r="D5" t="n">
-        <v>87.59643891142167</v>
+        <v>67.59332943739291</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.01143078621504</v>
+        <v>46.53091419048183</v>
       </c>
       <c r="C6" t="n">
-        <v>120.19144444012</v>
+        <v>146.4757757259199</v>
       </c>
       <c r="D6" t="n">
-        <v>57.11709968537519</v>
+        <v>48.38249036069132</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.22006002113408</v>
+        <v>37.18958478457343</v>
       </c>
       <c r="C7" t="n">
-        <v>121.0907253372101</v>
+        <v>149.057772188089</v>
       </c>
       <c r="D7" t="n">
-        <v>44.31609136970101</v>
+        <v>40.48334833232147</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.61870634232051</v>
+        <v>22.1138670381594</v>
       </c>
       <c r="C8" t="n">
-        <v>87.7044311588888</v>
+        <v>121.1673016581413</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.7578114166873</v>
+        <v>11.09374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>52.02968308196819</v>
+        <v>69.11405663127118</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
+        <v>40.14366362665208</v>
+      </c>
+      <c r="D10" t="n">
         <v>35.58835427894688</v>
-      </c>
-      <c r="D10" t="n">
-        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.885154890819568</v>
+        <v>7.873291509242248</v>
       </c>
       <c r="C21" t="n">
-        <v>103.4926579420068</v>
+        <v>102.3527896201492</v>
       </c>
       <c r="D21" t="n">
-        <v>9.85644361352446</v>
+        <v>9.841614386552809</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.150870351284519</v>
+        <v>7.237444075707486</v>
       </c>
       <c r="C2" t="n">
-        <v>8.709083884373454</v>
+        <v>8.271224408279377</v>
       </c>
       <c r="D2" t="n">
-        <v>26.15474058883927</v>
+        <v>35.28990297685585</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.15451960466102</v>
+        <v>19.03117924682442</v>
       </c>
       <c r="C3" t="n">
-        <v>24.02827506144068</v>
+        <v>29.8107690394544</v>
       </c>
       <c r="D3" t="n">
-        <v>86.79631453246051</v>
+        <v>70.5631162427395</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.07119422298706</v>
+        <v>33.70634392990574</v>
       </c>
       <c r="C4" t="n">
-        <v>56.27083316431443</v>
+        <v>91.26621182989624</v>
       </c>
       <c r="D4" t="n">
-        <v>127.4868116303781</v>
+        <v>95.78421476484006</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.63425974133501</v>
+        <v>45.9703362513569</v>
       </c>
       <c r="C5" t="n">
-        <v>83.15403054970486</v>
+        <v>146.9430876331414</v>
       </c>
       <c r="D5" t="n">
-        <v>103.1080526385213</v>
+        <v>79.86517574047804</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.22276858453534</v>
+        <v>51.4818678629985</v>
       </c>
       <c r="C6" t="n">
-        <v>122.8078020719378</v>
+        <v>169.6607295094126</v>
       </c>
       <c r="D6" t="n">
-        <v>68.2265567066321</v>
+        <v>55.6680400739069</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>51.2030515149924</v>
+        <v>44.73529763941441</v>
       </c>
       <c r="C7" t="n">
-        <v>145.3448023706275</v>
+        <v>175.1683341302372</v>
       </c>
       <c r="D7" t="n">
-        <v>49.82565948593412</v>
+        <v>43.95677170994669</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.29735604786232</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="C8" t="n">
-        <v>119.3314334511998</v>
+        <v>154.9639663768378</v>
       </c>
       <c r="D8" t="n">
-        <v>40.63944621729671</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.30468594568177</v>
+        <v>15.75312366234431</v>
       </c>
       <c r="C9" t="n">
-        <v>76.76874348128355</v>
+        <v>102.6171787863978</v>
       </c>
       <c r="D9" t="n">
-        <v>37.38593432542277</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.252972112526189</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>47.40368789955724</v>
+        <v>57.22607368054658</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>36.07235589714055</v>
+        <v>38.56010457970196</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.056082668173399</v>
+        <v>8.036875116384365</v>
       </c>
       <c r="C21" t="n">
-        <v>111.7781470209059</v>
+        <v>110.507032850285</v>
       </c>
       <c r="D21" t="n">
-        <v>11.07711366873842</v>
+        <v>11.0507032850285</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.278096642209105</v>
+        <v>6.640541471525426</v>
       </c>
       <c r="C2" t="n">
-        <v>5.782493978013713</v>
+        <v>5.690209693814514</v>
       </c>
       <c r="D2" t="n">
-        <v>21.38050150308704</v>
+        <v>28.90854289925158</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.46439202630452</v>
+        <v>23.04161861867264</v>
       </c>
       <c r="C3" t="n">
-        <v>37.50767104074939</v>
+        <v>47.73748211900116</v>
       </c>
       <c r="D3" t="n">
-        <v>95.62713513216056</v>
+        <v>75.66820430482291</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.24015263910875</v>
+        <v>22.07950586851077</v>
       </c>
       <c r="C4" t="n">
-        <v>73.37287817229387</v>
+        <v>123.2878766993145</v>
       </c>
       <c r="D4" t="n">
-        <v>120.9905870713769</v>
+        <v>91.22792366943061</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.48388811166922</v>
+        <v>28.98610096788708</v>
       </c>
       <c r="C5" t="n">
-        <v>73.36109719984292</v>
+        <v>101.3654504634832</v>
       </c>
       <c r="D5" t="n">
-        <v>69.45865007546185</v>
+        <v>54.73243451175969</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.79880814055419</v>
+        <v>27.77364255314227</v>
       </c>
       <c r="C6" t="n">
-        <v>95.71843766865554</v>
+        <v>115.3612457352257</v>
       </c>
       <c r="D6" t="n">
-        <v>32.80509953740717</v>
+        <v>28.94094057349173</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.69702517448201</v>
+        <v>19.64280806657018</v>
       </c>
       <c r="C7" t="n">
-        <v>83.90114055263666</v>
+        <v>108.9337435155218</v>
       </c>
       <c r="D7" t="n">
-        <v>28.56591295046944</v>
+        <v>28.20659329071511</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>56.57812019574367</v>
+        <v>75.60439070404686</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>36.16562192904399</v>
+        <v>43.59843379789659</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.18597658892593</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>26.4698816019025</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
         <v>23.96838845148163</v>
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.008876787067226</v>
+        <v>4.155738032076748</v>
       </c>
       <c r="C2" t="n">
-        <v>3.282964323001334</v>
+        <v>3.808199344773377</v>
       </c>
       <c r="D2" t="n">
-        <v>15.28973874593982</v>
+        <v>21.10266690278519</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.78484268851648</v>
+        <v>23.58157985600839</v>
       </c>
       <c r="C3" t="n">
-        <v>30.26237298340793</v>
+        <v>35.43618338478862</v>
       </c>
       <c r="D3" t="n">
-        <v>92.50517743265571</v>
+        <v>81.40161089762428</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.8287025400381</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="C4" t="n">
-        <v>86.25046280889927</v>
+        <v>124.6534877559218</v>
       </c>
       <c r="D4" t="n">
-        <v>139.2285141731699</v>
+        <v>104.5139153510027</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.55814108429348</v>
+        <v>32.32404316232624</v>
       </c>
       <c r="C5" t="n">
-        <v>103.9670818797373</v>
+        <v>160.147594255261</v>
       </c>
       <c r="D5" t="n">
-        <v>89.04451677518571</v>
+        <v>69.1641257641878</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.07806645691679</v>
+        <v>32.68434456978482</v>
       </c>
       <c r="C6" t="n">
-        <v>109.3234973541078</v>
+        <v>139.9550074743126</v>
       </c>
       <c r="D6" t="n">
-        <v>41.13719230334986</v>
+        <v>35.26045054572845</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.61906619521901</v>
+        <v>18.56484908730718</v>
       </c>
       <c r="C7" t="n">
-        <v>107.8557845362588</v>
+        <v>133.966346478407</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>75.43749359432491</v>
+        <v>99.72102305886976</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>28.12216298814988</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>42.04530892977813</v>
+        <v>48.7015583645715</v>
       </c>
       <c r="D9" t="n">
         <v>28.73281006019139</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.682355712180538</v>
+        <v>3.951534509593412</v>
       </c>
       <c r="C2" t="n">
-        <v>5.041274461307371</v>
+        <v>7.887361055918874</v>
       </c>
       <c r="D2" t="n">
-        <v>20.07674055184727</v>
+        <v>17.20905550774234</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.79127295408971</v>
+        <v>18.83482970597506</v>
       </c>
       <c r="C3" t="n">
-        <v>20.61179305066178</v>
+        <v>24.58787125286137</v>
       </c>
       <c r="D3" t="n">
-        <v>83.8265277271139</v>
+        <v>79.20740477863266</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.74984392852887</v>
+        <v>37.76488893926206</v>
       </c>
       <c r="C4" t="n">
-        <v>81.42615459023045</v>
+        <v>106.1347808107142</v>
       </c>
       <c r="D4" t="n">
-        <v>152.4889804144316</v>
+        <v>118.8081619248363</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.22206457427158</v>
+        <v>39.19627709205391</v>
       </c>
       <c r="C5" t="n">
-        <v>131.5051049838603</v>
+        <v>195.7604922268141</v>
       </c>
       <c r="D5" t="n">
-        <v>115.4780737120311</v>
+        <v>87.30191460014763</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.84034464376883</v>
+        <v>38.15856976866503</v>
       </c>
       <c r="C6" t="n">
-        <v>137.4594048101172</v>
+        <v>192.765179981157</v>
       </c>
       <c r="D6" t="n">
-        <v>56.67433147075987</v>
+        <v>46.0478943199924</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.73990327829938</v>
+        <v>26.52976821186155</v>
       </c>
       <c r="C7" t="n">
-        <v>131.9302017397991</v>
+        <v>167.2034150056828</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.60487975900305</v>
+        <v>13.35176877775662</v>
       </c>
       <c r="C8" t="n">
-        <v>107.6486357706628</v>
+        <v>135.5204530942297</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>65.67499442329461</v>
+        <v>80.31874317984003</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>39.85895679242051</v>
+        <v>43.41779222031519</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2467,7 +2467,7 @@
         <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.25291535926396</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.346777923777377</v>
+        <v>2.34539526544563</v>
       </c>
       <c r="C2" t="n">
-        <v>2.263910205993145</v>
+        <v>3.70904282664445</v>
       </c>
       <c r="D2" t="n">
-        <v>13.84067913447153</v>
+        <v>12.00088393671301</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.32141671438298</v>
+        <v>18.54030539470102</v>
       </c>
       <c r="C3" t="n">
-        <v>21.53463589265379</v>
+        <v>28.82902133520759</v>
       </c>
       <c r="D3" t="n">
-        <v>83.66453935591318</v>
+        <v>78.14220851952487</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.71454206890498</v>
+        <v>41.36397602303086</v>
       </c>
       <c r="C4" t="n">
-        <v>78.70769519717103</v>
+        <v>100.3277431400943</v>
       </c>
       <c r="D4" t="n">
-        <v>161.448409963388</v>
+        <v>128.8524226869854</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.23464736797755</v>
+        <v>41.01251034491051</v>
       </c>
       <c r="C5" t="n">
-        <v>155.2633994266331</v>
+        <v>228.5508655486575</v>
       </c>
       <c r="D5" t="n">
-        <v>125.4919002953486</v>
+        <v>92.55426481786806</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.31957639216151</v>
+        <v>31.95981476405067</v>
       </c>
       <c r="C6" t="n">
-        <v>170.7475242180138</v>
+        <v>229.3136835148573</v>
       </c>
       <c r="D6" t="n">
-        <v>55.54728510628455</v>
+        <v>45.60512610537709</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.30049691295753</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="C7" t="n">
-        <v>139.8951208643535</v>
+        <v>175.5276537899915</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>83.19820919639595</v>
+        <v>100.3051629428966</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39687241888974</v>
+        <v>33.05937219280708</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -2764,7 +2764,7 @@
         <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.96816746730337</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.776783418237479</v>
+        <v>2.617339379521997</v>
       </c>
       <c r="C2" t="n">
-        <v>2.626175108860218</v>
+        <v>7.690029767365266</v>
       </c>
       <c r="D2" t="n">
-        <v>17.9905266803228</v>
+        <v>10.77958979262998</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5438314748905</v>
+        <v>13.47939597930871</v>
       </c>
       <c r="C3" t="n">
-        <v>14.83420781116931</v>
+        <v>21.52972715413255</v>
       </c>
       <c r="D3" t="n">
-        <v>76.07072086356411</v>
+        <v>71.17179981937252</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.42176026886118</v>
+        <v>38.91353375323082</v>
       </c>
       <c r="C4" t="n">
-        <v>66.69797553111979</v>
+        <v>87.25871770116076</v>
       </c>
       <c r="D4" t="n">
-        <v>165.6856330549172</v>
+        <v>136.3441394180928</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.8255616749429</v>
+        <v>49.84823968313181</v>
       </c>
       <c r="C5" t="n">
-        <v>151.7045639987384</v>
+        <v>208.0568822225054</v>
       </c>
       <c r="D5" t="n">
-        <v>150.0846802867312</v>
+        <v>112.0910441323796</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.11331156327844</v>
+        <v>40.8151790563569</v>
       </c>
       <c r="C6" t="n">
-        <v>207.0142661605952</v>
+        <v>293.1528097312104</v>
       </c>
       <c r="D6" t="n">
-        <v>76.96116603131597</v>
+        <v>59.25043744670351</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.0382724649324</v>
+        <v>18.26541603751191</v>
       </c>
       <c r="C7" t="n">
-        <v>189.5411205204104</v>
+        <v>242.061677454502</v>
       </c>
       <c r="D7" t="n">
-        <v>41.14210104187108</v>
+        <v>37.90822410408209</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.842781498600267</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>126.341112059522</v>
+        <v>155.4646577060036</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>57.90937008270233</v>
+        <v>65.12030697039516</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.60978849752428</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.86995163914969</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.695879195861741</v>
+        <v>1.82506898219482</v>
       </c>
       <c r="C2" t="n">
-        <v>1.628719441345458</v>
+        <v>4.286310476741575</v>
       </c>
       <c r="D2" t="n">
-        <v>14.10967800543516</v>
+        <v>7.956083395216151</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.75214191464007</v>
+        <v>11.70243263462198</v>
       </c>
       <c r="C3" t="n">
-        <v>12.80689880189964</v>
+        <v>25.52053157189584</v>
       </c>
       <c r="D3" t="n">
-        <v>73.59671664886214</v>
+        <v>65.90963212460962</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.78889285252048</v>
+        <v>34.81670058340888</v>
       </c>
       <c r="C4" t="n">
-        <v>55.33915459298421</v>
+        <v>75.33833707619597</v>
       </c>
       <c r="D4" t="n">
-        <v>166.5407353053162</v>
+        <v>139.5858703375158</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.15783436733483</v>
+        <v>54.53608497091033</v>
       </c>
       <c r="C5" t="n">
-        <v>145.593184539802</v>
+        <v>197.4049196314274</v>
       </c>
       <c r="D5" t="n">
-        <v>167.8052263483861</v>
+        <v>125.5900750657732</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.4516957260741</v>
+        <v>47.65796055495717</v>
       </c>
       <c r="C6" t="n">
-        <v>228.9111669561161</v>
+        <v>319.8799092316256</v>
       </c>
       <c r="D6" t="n">
-        <v>92.13604029585892</v>
+        <v>71.04417261782045</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.43940636534185</v>
+        <v>16.5287043486993</v>
       </c>
       <c r="C7" t="n">
-        <v>232.5995930809713</v>
+        <v>301.8285141936394</v>
       </c>
       <c r="D7" t="n">
-        <v>46.71155576806323</v>
+        <v>41.74096714146164</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>161.6398507657161</v>
+        <v>201.528259989264</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>69.55780659359074</v>
+        <v>73.99530621678632</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.356996311447345</v>
+        <v>3.743403996293088</v>
       </c>
       <c r="C2" t="n">
-        <v>9.703594308775473</v>
+        <v>5.432010047597601</v>
       </c>
       <c r="D2" t="n">
-        <v>17.390678833028</v>
+        <v>10.29656992214055</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.55164439879547</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="C3" t="n">
-        <v>9.635853717182444</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D3" t="n">
-        <v>69.08067720932682</v>
+        <v>58.55143308127977</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.15227837181205</v>
+        <v>28.94584931201296</v>
       </c>
       <c r="C4" t="n">
-        <v>44.45255430059132</v>
+        <v>69.96523189085319</v>
       </c>
       <c r="D4" t="n">
-        <v>163.4393943076005</v>
+        <v>139.9177010615512</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.91239744127311</v>
+        <v>53.57888095926969</v>
       </c>
       <c r="C5" t="n">
-        <v>126.0073178400781</v>
+        <v>172.1003725544659</v>
       </c>
       <c r="D5" t="n">
-        <v>184.6421994762189</v>
+        <v>140.9544266372358</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>71.48694083243576</v>
+        <v>57.31835796474579</v>
       </c>
       <c r="C6" t="n">
-        <v>230.8432464380738</v>
+        <v>318.672359555402</v>
       </c>
       <c r="D6" t="n">
-        <v>115.5222523587222</v>
+        <v>86.94357668809754</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.16584291322225</v>
+        <v>29.76364514965055</v>
       </c>
       <c r="C7" t="n">
-        <v>277.0953442805495</v>
+        <v>369.4404968374129</v>
       </c>
       <c r="D7" t="n">
-        <v>57.73069200052944</v>
+        <v>48.80758711663017</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>220.4710819427062</v>
+        <v>276.548510809284</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>120.0343648074405</v>
+        <v>137.3406133379032</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>50.25075624187299</v>
+        <v>51.10487674456772</v>
       </c>
       <c r="D10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.857507714163971</v>
+        <v>5.153193699591508</v>
       </c>
       <c r="C2" t="n">
-        <v>3.50582105186536</v>
+        <v>6.54040320569225</v>
       </c>
       <c r="D2" t="n">
-        <v>12.7411217057151</v>
+        <v>5.055018929166827</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.085633034447725</v>
+        <v>2.704714925199963</v>
       </c>
       <c r="C2" t="n">
-        <v>5.434955290710342</v>
+        <v>3.128829933434584</v>
       </c>
       <c r="D2" t="n">
-        <v>12.79904482026567</v>
+        <v>7.660577336237862</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.16585860875548</v>
+        <v>12.85598618711198</v>
       </c>
       <c r="C3" t="n">
-        <v>19.78221624057323</v>
+        <v>24.45042657426681</v>
       </c>
       <c r="D3" t="n">
-        <v>75.50130719510095</v>
+        <v>62.70422587024377</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.57415214719769</v>
+        <v>40.50887377263189</v>
       </c>
       <c r="C4" t="n">
-        <v>65.0515846310979</v>
+        <v>100.8127265059922</v>
       </c>
       <c r="D4" t="n">
-        <v>169.6037881425662</v>
+        <v>142.5085332530585</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.77965621255477</v>
+        <v>33.28124717396688</v>
       </c>
       <c r="C5" t="n">
-        <v>191.0481032464293</v>
+        <v>264.9246179910018</v>
       </c>
       <c r="D5" t="n">
-        <v>169.228760519544</v>
+        <v>127.4553957038422</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.31200014796801</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="C6" t="n">
-        <v>232.252054393668</v>
+        <v>302.6522005175025</v>
       </c>
       <c r="D6" t="n">
-        <v>89.27817272879645</v>
+        <v>70.56115274733101</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.306166415004762</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>155.0464331839945</v>
+        <v>194.451822537053</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>88.45546815263761</v>
+        <v>101.2230970463674</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>38.2734342500619</v>
+        <v>38.93905919354123</v>
       </c>
       <c r="D9" t="n">
-        <v>20.96718571959912</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.776546738526</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4515,10 +4515,10 @@
         <v>6.998879383575511</v>
       </c>
       <c r="C2" t="n">
-        <v>7.418085653288899</v>
+        <v>8.283005380730339</v>
       </c>
       <c r="D2" t="n">
-        <v>16.32351907851172</v>
+        <v>8.941758090279949</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.56422719250143</v>
+        <v>10.95139564087317</v>
       </c>
       <c r="C3" t="n">
-        <v>8.83082059970006</v>
+        <v>16.73879835740812</v>
       </c>
       <c r="D3" t="n">
-        <v>13.83773389135879</v>
+        <v>7.584001015306611</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39803549338624</v>
+        <v>13.3991281086563</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1426564065515</v>
+        <v>70.1483765688477</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576239469810146</v>
+        <v>1.576368012783094</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.750677140850315</v>
+        <v>4.619122948481243</v>
       </c>
       <c r="C2" t="n">
-        <v>3.478332116146449</v>
+        <v>7.430848373444108</v>
       </c>
       <c r="D2" t="n">
-        <v>15.30741020461627</v>
+        <v>17.96892823082937</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.35653864755761</v>
+        <v>18.84955592153876</v>
       </c>
       <c r="C3" t="n">
-        <v>21.40209995258047</v>
+        <v>26.64463269325843</v>
       </c>
       <c r="D3" t="n">
-        <v>24.20498964820511</v>
+        <v>13.25850274585317</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.87231604518568</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="C4" t="n">
-        <v>14.01346673041897</v>
+        <v>26.45711888174729</v>
       </c>
       <c r="D4" t="n">
-        <v>22.32199755145973</v>
+        <v>19.04197847157113</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.092505268377454</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44135159779525</v>
+        <v>15.4441685279651</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14648786138403</v>
+        <v>86.16220336654213</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250810862693737</v>
+        <v>3.251403900624231</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.521929925760809</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C2" t="n">
-        <v>7.665486074759095</v>
+        <v>5.087416603406972</v>
       </c>
       <c r="D2" t="n">
-        <v>19.21476606751857</v>
+        <v>23.04358211408113</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.15251505152352</v>
+        <v>17.23948968657399</v>
       </c>
       <c r="C3" t="n">
-        <v>16.63080610994097</v>
+        <v>28.0239882177252</v>
       </c>
       <c r="D3" t="n">
-        <v>30.83178665187108</v>
+        <v>24.55351008321273</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.55845987946297</v>
+        <v>26.12528815771187</v>
       </c>
       <c r="C4" t="n">
-        <v>37.29266829351933</v>
+        <v>50.15749020996954</v>
       </c>
       <c r="D4" t="n">
-        <v>29.43083267791088</v>
+        <v>21.41584442043992</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.79984664152067</v>
+        <v>11.58462291011236</v>
       </c>
       <c r="C5" t="n">
-        <v>17.03332266868216</v>
+        <v>30.16419821298325</v>
       </c>
       <c r="D5" t="n">
-        <v>30.4587225242573</v>
+        <v>29.30516897176729</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5308,7 +5308,7 @@
         <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73736426026572</v>
+        <v>16.73937405032598</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0979219876209</v>
+        <v>102.1101817069885</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021209278079716</v>
+        <v>5.021812215097795</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.01124119310322</v>
+        <v>5.268058180988385</v>
       </c>
       <c r="C2" t="n">
-        <v>5.641122308602172</v>
+        <v>4.762458113301277</v>
       </c>
       <c r="D2" t="n">
-        <v>32.29655422660732</v>
+        <v>21.5159826862731</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.69461971071701</v>
+        <v>15.11891464540088</v>
       </c>
       <c r="C3" t="n">
-        <v>24.49951395947915</v>
+        <v>23.23305942100077</v>
       </c>
       <c r="D3" t="n">
-        <v>38.57777603837842</v>
+        <v>36.60446315284232</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.49388551516093</v>
+        <v>30.18383316706819</v>
       </c>
       <c r="C4" t="n">
-        <v>39.34746623850791</v>
+        <v>61.3121076256218</v>
       </c>
       <c r="D4" t="n">
-        <v>37.49687181600267</v>
+        <v>28.49915410658066</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.91876128692155</v>
+        <v>25.2554596917492</v>
       </c>
       <c r="C5" t="n">
-        <v>45.52854978444584</v>
+        <v>63.59270754258716</v>
       </c>
       <c r="D5" t="n">
-        <v>34.28753857081986</v>
+        <v>30.16419821298325</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.96103319146639</v>
+        <v>10.86794708601219</v>
       </c>
       <c r="C6" t="n">
-        <v>20.04532462531138</v>
+        <v>30.95352336719769</v>
       </c>
       <c r="D6" t="n">
-        <v>38.56108632740622</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
         <v>46.86470840992573</v>
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06748658905851</v>
+        <v>18.06636702051607</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8688410810008</v>
+        <v>117.861537229081</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882852033927053</v>
+        <v>6.882425531625169</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.552184178143213</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="C2" t="n">
-        <v>3.800345363139403</v>
+        <v>10.46641227497525</v>
       </c>
       <c r="D2" t="n">
-        <v>38.02112509007048</v>
+        <v>21.19200594387165</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.0529576227671</v>
+        <v>14.92747384307275</v>
       </c>
       <c r="C3" t="n">
-        <v>21.61808444751476</v>
+        <v>19.27170743436489</v>
       </c>
       <c r="D3" t="n">
-        <v>51.30613502393831</v>
+        <v>42.16115515887927</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.41959148480766</v>
+        <v>21.45413258090555</v>
       </c>
       <c r="C4" t="n">
-        <v>42.93379060212151</v>
+        <v>49.3406761200362</v>
       </c>
       <c r="D4" t="n">
-        <v>41.38950146334128</v>
+        <v>34.72736154232243</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.17553721707771</v>
+        <v>21.67208057124834</v>
       </c>
       <c r="C5" t="n">
-        <v>44.89041377668541</v>
+        <v>67.49515466696822</v>
       </c>
       <c r="D5" t="n">
-        <v>32.54493639578177</v>
+        <v>26.89988709636261</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.77235770580176</v>
+        <v>12.47801332097696</v>
       </c>
       <c r="C6" t="n">
-        <v>31.87931145230244</v>
+        <v>45.72588107299945</v>
       </c>
       <c r="D6" t="n">
-        <v>31.63780151705772</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>16.28915790886308</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.66194429903638</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5916,7 +5916,7 @@
         <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.062979839451885</v>
+        <v>7.061645812878435</v>
       </c>
       <c r="C21" t="n">
-        <v>66.21543599486142</v>
+        <v>66.20292949573533</v>
       </c>
       <c r="D21" t="n">
-        <v>5.297234879588914</v>
+        <v>5.296234359658826</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.606180301876787</v>
+        <v>4.715334223497431</v>
       </c>
       <c r="C2" t="n">
-        <v>3.817035074111599</v>
+        <v>9.279479300540853</v>
       </c>
       <c r="D2" t="n">
-        <v>26.63481521621597</v>
+        <v>23.56685364044468</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.7148765596077</v>
+        <v>17.68127615348505</v>
       </c>
       <c r="C3" t="n">
-        <v>17.19531103988288</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D3" t="n">
-        <v>71.87374942790899</v>
+        <v>50.21639507222435</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.78818884225672</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="C4" t="n">
-        <v>50.19577837043517</v>
+        <v>48.77911643320702</v>
       </c>
       <c r="D4" t="n">
-        <v>59.55085224420302</v>
+        <v>49.48106604174349</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.72870314292517</v>
+        <v>27.93072218582176</v>
       </c>
       <c r="C5" t="n">
-        <v>66.3661448070844</v>
+        <v>82.39317607891357</v>
       </c>
       <c r="D5" t="n">
-        <v>41.03705403751668</v>
+        <v>34.11573272257667</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.39879485656924</v>
+        <v>22.37992066601029</v>
       </c>
       <c r="C6" t="n">
-        <v>55.50703345041042</v>
+        <v>82.55614619781855</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>32.32207966691774</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.69596131131975</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="C7" t="n">
-        <v>33.95570784678443</v>
+        <v>47.78951474732623</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>20.86213871524472</v>
+        <v>24.53387512912779</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6227,7 +6227,7 @@
         <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.287257310770512</v>
+        <v>7.285720912365288</v>
       </c>
       <c r="C21" t="n">
-        <v>75.60529459924406</v>
+        <v>75.58935446578987</v>
       </c>
       <c r="D21" t="n">
-        <v>6.376350146924198</v>
+        <v>6.375005798319627</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.323036052426207</v>
+        <v>5.584180941755857</v>
       </c>
       <c r="C2" t="n">
-        <v>6.510950774564847</v>
+        <v>13.77392029058275</v>
       </c>
       <c r="D2" t="n">
-        <v>27.7029567184365</v>
+        <v>20.58724935805562</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.03532722181966</v>
+        <v>16.92042168269378</v>
       </c>
       <c r="C3" t="n">
-        <v>15.76195939168254</v>
+        <v>35.06311925717483</v>
       </c>
       <c r="D3" t="n">
-        <v>76.5026898534327</v>
+        <v>57.41751448287471</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.13126075939537</v>
+        <v>30.91130821591507</v>
       </c>
       <c r="C4" t="n">
-        <v>45.98408071921636</v>
+        <v>69.39090948386881</v>
       </c>
       <c r="D4" t="n">
-        <v>81.60483267240336</v>
+        <v>63.53282093262809</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.4599663138688</v>
+        <v>34.72932503773092</v>
       </c>
       <c r="C5" t="n">
-        <v>81.77958376375932</v>
+        <v>86.12381735505146</v>
       </c>
       <c r="D5" t="n">
-        <v>53.8979489631499</v>
+        <v>43.88412237983243</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.83276839957533</v>
       </c>
       <c r="C6" t="n">
-        <v>83.52218593879741</v>
+        <v>109.8467688804714</v>
       </c>
       <c r="D6" t="n">
-        <v>40.41266249761571</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.27781890476862</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>59.28774385946488</v>
+        <v>87.43445054022094</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>35.09355343600648</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>34.54770171244525</v>
+        <v>45.89670517353839</v>
       </c>
       <c r="D8" t="n">
         <v>34.38080460272329</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.500177730469495</v>
+        <v>7.496911100087268</v>
       </c>
       <c r="C21" t="n">
-        <v>85.31452168409051</v>
+        <v>85.27736376349267</v>
       </c>
       <c r="D21" t="n">
-        <v>7.500177730469495</v>
+        <v>7.496911100087268</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_54_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_54_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497619611139</v>
+        <v>10.84497635120521</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907146765939</v>
+        <v>37.78907200808023</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.991606239018283</v>
+        <v>6.200718500022854</v>
       </c>
       <c r="C2" t="n">
-        <v>6.665085164131596</v>
+        <v>11.32249627307846</v>
       </c>
       <c r="D2" t="n">
-        <v>26.30494798758903</v>
+        <v>22.93755336202248</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.20160243673586</v>
+        <v>20.45471341798229</v>
       </c>
       <c r="C3" t="n">
-        <v>45.44510122958485</v>
+        <v>27.82763867687584</v>
       </c>
       <c r="D3" t="n">
-        <v>60.84381397069607</v>
+        <v>64.14739499548659</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.61325782445154</v>
+        <v>43.3677230873986</v>
       </c>
       <c r="C4" t="n">
-        <v>79.43517024601793</v>
+        <v>59.39769960234052</v>
       </c>
       <c r="D4" t="n">
-        <v>75.79779500178348</v>
+        <v>80.81354402278045</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.57072387799944</v>
+        <v>50.63363784652926</v>
       </c>
       <c r="C5" t="n">
-        <v>108.3849465488479</v>
+        <v>117.7360934317988</v>
       </c>
       <c r="D5" t="n">
-        <v>56.05779391249288</v>
+        <v>60.13204688511715</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.40637110076273</v>
+        <v>45.36361617013237</v>
       </c>
       <c r="C6" t="n">
-        <v>122.9688086954342</v>
+        <v>148.890875078367</v>
       </c>
       <c r="D6" t="n">
-        <v>41.13719230334986</v>
+        <v>44.27682146153116</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.14670668075605</v>
+        <v>31.79978988825843</v>
       </c>
       <c r="C7" t="n">
-        <v>124.6240353247943</v>
+        <v>147.1414006693992</v>
       </c>
       <c r="D7" t="n">
-        <v>37.84833749412304</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.18763698469816</v>
+        <v>16.10557108816892</v>
       </c>
       <c r="C8" t="n">
-        <v>81.52923809917637</v>
+        <v>102.0575825949772</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>42.3781214015178</v>
+        <v>52.36249555370786</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
         <v>34.73423377625215</v>
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.693284055936877</v>
+        <v>7.651435643572737</v>
       </c>
       <c r="C21" t="n">
-        <v>94.24272968522673</v>
+        <v>92.77365717831944</v>
       </c>
       <c r="D21" t="n">
-        <v>8.654944562928987</v>
+        <v>7.651435643572737</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.846307578789756</v>
+        <v>6.519786503903068</v>
       </c>
       <c r="C2" t="n">
-        <v>6.253732876052181</v>
+        <v>14.51513980728909</v>
       </c>
       <c r="D2" t="n">
-        <v>27.35443628342888</v>
+        <v>21.9145722541973</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.21280257211008</v>
+        <v>20.37617360164255</v>
       </c>
       <c r="C3" t="n">
-        <v>35.14165907351457</v>
+        <v>35.62762418711675</v>
       </c>
       <c r="D3" t="n">
-        <v>66.36614480708438</v>
+        <v>66.40541471525425</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.68532631748906</v>
+        <v>40.66202641449439</v>
       </c>
       <c r="C4" t="n">
-        <v>96.35853717182444</v>
+        <v>63.5583463729385</v>
       </c>
       <c r="D4" t="n">
-        <v>86.93964969728053</v>
+        <v>90.7812284639983</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.56505437595222</v>
+        <v>57.18680377237672</v>
       </c>
       <c r="C5" t="n">
-        <v>125.5164439879547</v>
+        <v>113.6863841517807</v>
       </c>
       <c r="D5" t="n">
-        <v>67.59332943739291</v>
+        <v>72.91931073293185</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.53091419048183</v>
+        <v>55.18502020341747</v>
       </c>
       <c r="C6" t="n">
-        <v>146.4757757259199</v>
+        <v>165.1122923956371</v>
       </c>
       <c r="D6" t="n">
-        <v>48.38249036069132</v>
+        <v>51.07935130425731</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.18958478457343</v>
+        <v>41.50142070162541</v>
       </c>
       <c r="C7" t="n">
-        <v>149.057772188089</v>
+        <v>179.1208503875348</v>
       </c>
       <c r="D7" t="n">
-        <v>40.48334833232147</v>
+        <v>42.16017341117502</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.1138670381594</v>
+        <v>24.11663235482289</v>
       </c>
       <c r="C8" t="n">
-        <v>121.1673016581413</v>
+        <v>143.3646172511617</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.09374905798895</v>
+        <v>11.6484365108884</v>
       </c>
       <c r="C9" t="n">
-        <v>69.11405663127118</v>
+        <v>85.75468021825461</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>40.14366362665208</v>
+        <v>44.84132639147307</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.873291509242248</v>
+        <v>7.823524144610053</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3527896201492</v>
+        <v>100.7278733618544</v>
       </c>
       <c r="D21" t="n">
-        <v>9.841614386552809</v>
+        <v>8.80146466268631</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.237444075707486</v>
+        <v>7.314020396638737</v>
       </c>
       <c r="C2" t="n">
-        <v>8.271224408279377</v>
+        <v>15.92394776288326</v>
       </c>
       <c r="D2" t="n">
-        <v>35.28990297685585</v>
+        <v>23.61692277336127</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.03117924682442</v>
+        <v>20.4988920646734</v>
       </c>
       <c r="C3" t="n">
-        <v>29.8107690394544</v>
+        <v>44.69897297435728</v>
       </c>
       <c r="D3" t="n">
-        <v>70.5631162427395</v>
+        <v>67.3331662957675</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.70634392990574</v>
+        <v>38.76038111136832</v>
       </c>
       <c r="C4" t="n">
-        <v>91.26621182989624</v>
+        <v>74.50876026610743</v>
       </c>
       <c r="D4" t="n">
-        <v>95.78421476484006</v>
+        <v>99.80447161373074</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.9703362513569</v>
+        <v>58.16855147662353</v>
       </c>
       <c r="C5" t="n">
-        <v>146.9430876331414</v>
+        <v>113.6618404591745</v>
       </c>
       <c r="D5" t="n">
-        <v>79.86517574047804</v>
+        <v>83.64490440182826</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.4818678629985</v>
+        <v>63.59761628110839</v>
       </c>
       <c r="C6" t="n">
-        <v>169.6607295094126</v>
+        <v>170.465762626895</v>
       </c>
       <c r="D6" t="n">
-        <v>55.6680400739069</v>
+        <v>59.08943082320704</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.73529763941441</v>
+        <v>51.08327829507428</v>
       </c>
       <c r="C7" t="n">
-        <v>175.1683341302372</v>
+        <v>205.1116391097649</v>
       </c>
       <c r="D7" t="n">
-        <v>43.95677170994669</v>
+        <v>46.35223610830891</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.6242369756475</v>
+        <v>32.46148784092078</v>
       </c>
       <c r="C8" t="n">
-        <v>154.9639663768378</v>
+        <v>181.4171582677681</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>39.38771789438203</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.75312366234431</v>
+        <v>16.75156107756332</v>
       </c>
       <c r="C9" t="n">
-        <v>102.6171787863978</v>
+        <v>122.8078020719377</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>57.22607368054658</v>
+        <v>67.76022654711485</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56010457970196</v>
+        <v>39.98167525545134</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.036875116384365</v>
+        <v>7.979665933420957</v>
       </c>
       <c r="C21" t="n">
-        <v>110.507032850285</v>
+        <v>107.7254901011829</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0507032850285</v>
+        <v>9.974582416776197</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.640541471525426</v>
+        <v>6.803511590430396</v>
       </c>
       <c r="C2" t="n">
-        <v>5.690209693814514</v>
+        <v>11.08294983324224</v>
       </c>
       <c r="D2" t="n">
-        <v>28.90854289925158</v>
+        <v>19.53972455762426</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.04161861867264</v>
+        <v>25.44690049407733</v>
       </c>
       <c r="C3" t="n">
-        <v>47.73748211900116</v>
+        <v>63.29327449279187</v>
       </c>
       <c r="D3" t="n">
-        <v>75.66820430482291</v>
+        <v>73.19910882864218</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.07950586851077</v>
+        <v>27.93759441975148</v>
       </c>
       <c r="C4" t="n">
-        <v>123.2878766993145</v>
+        <v>96.79246965710152</v>
       </c>
       <c r="D4" t="n">
-        <v>91.22792366943061</v>
+        <v>95.20989235785567</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.98610096788708</v>
+        <v>35.80924751240241</v>
       </c>
       <c r="C5" t="n">
-        <v>101.3654504634832</v>
+        <v>101.8563243156066</v>
       </c>
       <c r="D5" t="n">
-        <v>54.73243451175969</v>
+        <v>57.7758523949248</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.77364255314227</v>
+        <v>31.71830482880595</v>
       </c>
       <c r="C6" t="n">
-        <v>115.3612457352257</v>
+        <v>135.0845571135441</v>
       </c>
       <c r="D6" t="n">
-        <v>28.94094057349173</v>
+        <v>30.51075515258238</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.64280806657018</v>
+        <v>21.4992929753009</v>
       </c>
       <c r="C7" t="n">
-        <v>108.9337435155218</v>
+        <v>127.5584792127881</v>
       </c>
       <c r="D7" t="n">
-        <v>28.20659329071511</v>
+        <v>27.66761380108361</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>11.59934912567606</v>
       </c>
       <c r="C8" t="n">
-        <v>75.60439070404686</v>
+        <v>90.45823346930109</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>43.59843379789659</v>
+        <v>51.69687061022852</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.155738032076748</v>
+        <v>4.363868545377072</v>
       </c>
       <c r="C2" t="n">
-        <v>3.808199344773377</v>
+        <v>5.140430979436299</v>
       </c>
       <c r="D2" t="n">
-        <v>21.10266690278519</v>
+        <v>13.38122120888403</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.58157985600839</v>
+        <v>25.13764996723958</v>
       </c>
       <c r="C3" t="n">
-        <v>35.43618338478862</v>
+        <v>54.36918786118836</v>
       </c>
       <c r="D3" t="n">
-        <v>81.40161089762428</v>
+        <v>73.01748550335653</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.46010518258904</v>
+        <v>36.68005772606933</v>
       </c>
       <c r="C4" t="n">
-        <v>124.6534877559218</v>
+        <v>129.0693889296239</v>
       </c>
       <c r="D4" t="n">
-        <v>104.5139153510027</v>
+        <v>106.9133067401819</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.32404316232624</v>
+        <v>40.07985002587604</v>
       </c>
       <c r="C5" t="n">
-        <v>160.147594255261</v>
+        <v>136.8065425867931</v>
       </c>
       <c r="D5" t="n">
-        <v>69.1641257641878</v>
+        <v>73.31200981463057</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.68434456978482</v>
+        <v>37.39378830705677</v>
       </c>
       <c r="C6" t="n">
-        <v>139.9550074743126</v>
+        <v>154.0833386861284</v>
       </c>
       <c r="D6" t="n">
-        <v>35.26045054572845</v>
+        <v>36.58875518957439</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.56484908730718</v>
+        <v>20.12190094624263</v>
       </c>
       <c r="C7" t="n">
-        <v>133.966346478407</v>
+        <v>156.1842787732166</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>30.06307819944583</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>99.72102305886976</v>
+        <v>118.1631536831461</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>48.7015583645715</v>
+        <v>55.35780779936488</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
         <v>28.20561154301086</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.951534509593412</v>
+        <v>4.109595889977149</v>
       </c>
       <c r="C2" t="n">
-        <v>7.887361055918874</v>
+        <v>8.61189086165302</v>
       </c>
       <c r="D2" t="n">
-        <v>17.20905550774234</v>
+        <v>17.99936240966102</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.83482970597506</v>
+        <v>20.00310947402876</v>
       </c>
       <c r="C3" t="n">
-        <v>24.58787125286137</v>
+        <v>36.37375244234433</v>
       </c>
       <c r="D3" t="n">
-        <v>79.20740477863266</v>
+        <v>67.27917017203391</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.76488893926206</v>
+        <v>41.64475586644545</v>
       </c>
       <c r="C4" t="n">
-        <v>106.1347808107142</v>
+        <v>133.5108155436365</v>
       </c>
       <c r="D4" t="n">
-        <v>118.8081619248363</v>
+        <v>117.1872964651248</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.19627709205391</v>
+        <v>46.90299657039137</v>
       </c>
       <c r="C5" t="n">
-        <v>195.7604922268141</v>
+        <v>184.224956701914</v>
       </c>
       <c r="D5" t="n">
-        <v>87.30191460014763</v>
+        <v>91.40071126537806</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.15856976866503</v>
+        <v>45.08185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>192.765179981157</v>
+        <v>182.984027603746</v>
       </c>
       <c r="D6" t="n">
-        <v>46.0478943199924</v>
+        <v>48.1409804254466</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.52976821186155</v>
+        <v>29.2845522699781</v>
       </c>
       <c r="C7" t="n">
-        <v>167.2034150056828</v>
+        <v>188.4032749311884</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.35176877775662</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="C8" t="n">
-        <v>135.5204530942297</v>
+        <v>158.2184600164159</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>80.31874317984003</v>
+        <v>92.74374212478766</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>43.41779222031519</v>
+        <v>46.40721397974673</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.34539526544563</v>
+        <v>2.516219365984575</v>
       </c>
       <c r="C2" t="n">
-        <v>3.70904282664445</v>
+        <v>4.191080949429634</v>
       </c>
       <c r="D2" t="n">
-        <v>12.00088393671301</v>
+        <v>12.55262614649972</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.54030539470102</v>
+        <v>19.43369580556561</v>
       </c>
       <c r="C3" t="n">
-        <v>28.82902133520759</v>
+        <v>37.52239725631309</v>
       </c>
       <c r="D3" t="n">
-        <v>78.14220851952487</v>
+        <v>68.13329067472864</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.36397602303086</v>
+        <v>45.7543517564226</v>
       </c>
       <c r="C4" t="n">
-        <v>100.3277431400943</v>
+        <v>131.5836448002</v>
       </c>
       <c r="D4" t="n">
-        <v>128.8524226869854</v>
+        <v>124.6917759163874</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.01251034491051</v>
+        <v>48.27744335633691</v>
       </c>
       <c r="C5" t="n">
-        <v>228.5508655486575</v>
+        <v>226.7100886031947</v>
       </c>
       <c r="D5" t="n">
-        <v>92.55426481786806</v>
+        <v>96.50579932746149</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.95981476405067</v>
+        <v>36.06548366321083</v>
       </c>
       <c r="C6" t="n">
-        <v>229.3136835148573</v>
+        <v>220.5388225342993</v>
       </c>
       <c r="D6" t="n">
-        <v>45.60512610537709</v>
+        <v>47.41645061971246</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.803331663981149</v>
+        <v>9.282424543653592</v>
       </c>
       <c r="C7" t="n">
-        <v>175.5276537899915</v>
+        <v>199.7218442134499</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>100.3051629428966</v>
+        <v>114.8252114887069</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>33.05937219280708</v>
+        <v>35.38905949498476</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.617339379521997</v>
+        <v>3.157300616857742</v>
       </c>
       <c r="C2" t="n">
-        <v>7.690029767365266</v>
+        <v>10.54200684820225</v>
       </c>
       <c r="D2" t="n">
-        <v>10.77958979262998</v>
+        <v>15.84638969424777</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.47939597930871</v>
+        <v>14.28933783531232</v>
       </c>
       <c r="C3" t="n">
-        <v>21.52972715413255</v>
+        <v>26.94406574305371</v>
       </c>
       <c r="D3" t="n">
-        <v>71.17179981937252</v>
+        <v>62.97420648891165</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.91353375323082</v>
+        <v>42.07868835172254</v>
       </c>
       <c r="C4" t="n">
-        <v>87.25871770116076</v>
+        <v>114.4305489115997</v>
       </c>
       <c r="D4" t="n">
-        <v>136.3441394180928</v>
+        <v>128.954524448227</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.84823968313181</v>
+        <v>56.69592992025331</v>
       </c>
       <c r="C5" t="n">
-        <v>208.0568822225054</v>
+        <v>235.545817941416</v>
       </c>
       <c r="D5" t="n">
-        <v>112.0910441323796</v>
+        <v>114.2018016965102</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.8151790563569</v>
+        <v>46.57116584635595</v>
       </c>
       <c r="C6" t="n">
-        <v>293.1528097312104</v>
+        <v>281.7213394629605</v>
       </c>
       <c r="D6" t="n">
-        <v>59.25043744670351</v>
+        <v>62.14855666964009</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.26541603751191</v>
+        <v>19.70269467652924</v>
       </c>
       <c r="C7" t="n">
-        <v>242.061677454502</v>
+        <v>252.6017208072958</v>
       </c>
       <c r="D7" t="n">
-        <v>37.90822410408209</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>155.4646577060036</v>
+        <v>173.0723027816702</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>65.12030697039516</v>
+        <v>71.66561891460864</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.08946221427348</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.60978849752428</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.82506898219482</v>
+        <v>2.411172361630166</v>
       </c>
       <c r="C2" t="n">
-        <v>4.286310476741575</v>
+        <v>6.406885517914684</v>
       </c>
       <c r="D2" t="n">
-        <v>7.956083395216151</v>
+        <v>11.21254053020282</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.70243263462198</v>
+        <v>12.92961726493049</v>
       </c>
       <c r="C3" t="n">
-        <v>25.52053157189584</v>
+        <v>33.64940256305943</v>
       </c>
       <c r="D3" t="n">
-        <v>65.90963212460962</v>
+        <v>61.4672237628928</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.81670058340888</v>
+        <v>37.17780381212246</v>
       </c>
       <c r="C4" t="n">
-        <v>75.33833707619597</v>
+        <v>97.2008767020682</v>
       </c>
       <c r="D4" t="n">
-        <v>139.5858703375158</v>
+        <v>130.6009153482489</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.53608497091033</v>
+        <v>61.08925089675779</v>
       </c>
       <c r="C5" t="n">
-        <v>197.4049196314274</v>
+        <v>234.3186333111075</v>
       </c>
       <c r="D5" t="n">
-        <v>125.5900750657732</v>
+        <v>127.0381529295373</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.65796055495717</v>
+        <v>53.69570893607505</v>
       </c>
       <c r="C6" t="n">
-        <v>319.8799092316256</v>
+        <v>323.8245715072892</v>
       </c>
       <c r="D6" t="n">
-        <v>71.04417261782045</v>
+        <v>72.2114706381699</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.5287043486993</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="C7" t="n">
-        <v>301.8285141936394</v>
+        <v>307.3380823098724</v>
       </c>
       <c r="D7" t="n">
-        <v>41.74096714146164</v>
+        <v>41.32176087174825</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>201.528259989264</v>
+        <v>215.9648599802133</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>73.99530621678632</v>
+        <v>78.32186834940201</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.743403996293088</v>
+        <v>3.642283982755667</v>
       </c>
       <c r="C2" t="n">
-        <v>5.432010047597601</v>
+        <v>5.716716881829178</v>
       </c>
       <c r="D2" t="n">
-        <v>10.29656992214055</v>
+        <v>13.76999329976576</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.105709956889166</v>
+        <v>10.64214511403542</v>
       </c>
       <c r="C3" t="n">
-        <v>21.25974653546468</v>
+        <v>29.49660977409542</v>
       </c>
       <c r="D3" t="n">
-        <v>58.55143308127977</v>
+        <v>57.02481540117598</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.94584931201296</v>
+        <v>31.26866438026091</v>
       </c>
       <c r="C4" t="n">
-        <v>69.96523189085319</v>
+        <v>91.25344910974103</v>
       </c>
       <c r="D4" t="n">
-        <v>139.9177010615512</v>
+        <v>130.5498644676281</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.57888095926969</v>
+        <v>59.56754195517523</v>
       </c>
       <c r="C5" t="n">
-        <v>172.1003725544659</v>
+        <v>211.2230185687013</v>
       </c>
       <c r="D5" t="n">
-        <v>140.9544266372358</v>
+        <v>137.4446785945535</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.31835796474579</v>
+        <v>63.03409309887072</v>
       </c>
       <c r="C6" t="n">
-        <v>318.672359555402</v>
+        <v>343.2661212944888</v>
       </c>
       <c r="D6" t="n">
-        <v>86.94357668809754</v>
+        <v>88.27188133194348</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.76364514965055</v>
+        <v>32.09922293805371</v>
       </c>
       <c r="C7" t="n">
-        <v>369.4404968374129</v>
+        <v>368.7218575179043</v>
       </c>
       <c r="D7" t="n">
-        <v>48.80758711663017</v>
+        <v>48.62792728675301</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>276.548510809284</v>
+        <v>288.648551264126</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>137.3406133379032</v>
+        <v>141.6671754705189</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>51.10487674456772</v>
+        <v>51.95899724726245</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.153193699591508</v>
+        <v>7.032258805519903</v>
       </c>
       <c r="C2" t="n">
-        <v>6.54040320569225</v>
+        <v>11.75642875835555</v>
       </c>
       <c r="D2" t="n">
-        <v>5.055018929166827</v>
+        <v>9.52295273119406</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.704714925199963</v>
+        <v>2.661518026213103</v>
       </c>
       <c r="C2" t="n">
-        <v>3.128829933434584</v>
+        <v>3.384084336538756</v>
       </c>
       <c r="D2" t="n">
-        <v>7.660577336237862</v>
+        <v>10.24453729381547</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.85598618711198</v>
+        <v>14.3727863901733</v>
       </c>
       <c r="C3" t="n">
-        <v>24.45042657426681</v>
+        <v>32.32895190084746</v>
       </c>
       <c r="D3" t="n">
-        <v>62.70422587024377</v>
+        <v>62.45388020566084</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.50887377263189</v>
+        <v>44.58018150214342</v>
       </c>
       <c r="C4" t="n">
-        <v>100.8127265059922</v>
+        <v>129.5160841350562</v>
       </c>
       <c r="D4" t="n">
-        <v>142.5085332530585</v>
+        <v>132.4515097707542</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.28124717396688</v>
+        <v>36.05468443846411</v>
       </c>
       <c r="C5" t="n">
-        <v>264.9246179910018</v>
+        <v>299.9975547252191</v>
       </c>
       <c r="D5" t="n">
-        <v>127.4553957038422</v>
+        <v>125.8600556844411</v>
       </c>
     </row>
     <row r="6">
@@ -4257,10 +4257,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.47551004622073</v>
+        <v>19.92456965768902</v>
       </c>
       <c r="C6" t="n">
-        <v>302.6522005175025</v>
+        <v>303.4169819791107</v>
       </c>
       <c r="D6" t="n">
         <v>70.56115274733101</v>
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>194.451822537053</v>
+        <v>202.9557211512388</v>
       </c>
       <c r="D7" t="n">
-        <v>31.73990327829938</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>101.2230970463674</v>
+        <v>104.3941421310846</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>38.93905919354123</v>
+        <v>39.60468413702056</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>15.28188476430585</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>12.80100831567416</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.998879383575511</v>
+        <v>7.336600593836414</v>
       </c>
       <c r="C2" t="n">
-        <v>8.283005380730339</v>
+        <v>10.54789733442773</v>
       </c>
       <c r="D2" t="n">
-        <v>8.941758090279949</v>
+        <v>14.54851922923348</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.95139564087317</v>
+        <v>14.93238258159398</v>
       </c>
       <c r="C3" t="n">
-        <v>16.73879835740812</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D3" t="n">
-        <v>7.584001015306611</v>
+        <v>11.13301896615883</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3991281086563</v>
+        <v>13.39714255714293</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1483765688477</v>
+        <v>70.13798162268945</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576368012783094</v>
+        <v>1.576134418487403</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.619122948481243</v>
+        <v>5.250386722311942</v>
       </c>
       <c r="C2" t="n">
-        <v>7.430848373444108</v>
+        <v>4.73104218676538</v>
       </c>
       <c r="D2" t="n">
-        <v>17.96892823082937</v>
+        <v>18.1456428175938</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.84955592153876</v>
+        <v>21.19593293468864</v>
       </c>
       <c r="C3" t="n">
-        <v>26.64463269325843</v>
+        <v>36.82535638629786</v>
       </c>
       <c r="D3" t="n">
-        <v>13.25850274585317</v>
+        <v>20.66088043587412</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.80100831567416</v>
+        <v>17.30624853046277</v>
       </c>
       <c r="C4" t="n">
-        <v>26.45711888174729</v>
+        <v>45.69053815564656</v>
       </c>
       <c r="D4" t="n">
-        <v>19.04197847157113</v>
+        <v>20.90533561423158</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4441685279651</v>
+        <v>15.43652664345976</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16220336654213</v>
+        <v>86.11956969509131</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251403900624231</v>
+        <v>3.249795082833634</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.902447124381071</v>
+        <v>5.42317431825938</v>
       </c>
       <c r="C2" t="n">
-        <v>5.087416603406972</v>
+        <v>5.811946409141117</v>
       </c>
       <c r="D2" t="n">
-        <v>23.04358211408113</v>
+        <v>18.61197297711103</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.23948968657399</v>
+        <v>19.46805697521425</v>
       </c>
       <c r="C3" t="n">
-        <v>28.0239882177252</v>
+        <v>25.81996462169111</v>
       </c>
       <c r="D3" t="n">
-        <v>24.55351008321273</v>
+        <v>30.38018270791754</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.12528815771187</v>
+        <v>30.3497485290859</v>
       </c>
       <c r="C4" t="n">
-        <v>50.15749020996954</v>
+        <v>72.60711496298136</v>
       </c>
       <c r="D4" t="n">
-        <v>21.41584442043992</v>
+        <v>26.55922064298896</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.58462291011236</v>
+        <v>14.87347771933918</v>
       </c>
       <c r="C5" t="n">
-        <v>30.16419821298325</v>
+        <v>49.60280275707011</v>
       </c>
       <c r="D5" t="n">
-        <v>29.30516897176729</v>
+        <v>30.4587225242573</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
         <v>31.45225120095506</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73937405032598</v>
+        <v>16.72298322698279</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1101817069885</v>
+        <v>102.0101976845951</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021812215097795</v>
+        <v>4.180745806745699</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.268058180988385</v>
+        <v>6.723990026386404</v>
       </c>
       <c r="C2" t="n">
-        <v>4.762458113301277</v>
+        <v>9.830239762623313</v>
       </c>
       <c r="D2" t="n">
-        <v>21.5159826862731</v>
+        <v>26.72513600500667</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.11891464540088</v>
+        <v>18.93300447639974</v>
       </c>
       <c r="C3" t="n">
-        <v>23.23305942100077</v>
+        <v>23.93991776805847</v>
       </c>
       <c r="D3" t="n">
-        <v>36.60446315284232</v>
+        <v>37.76783418237479</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.18383316706819</v>
+        <v>34.30619177720055</v>
       </c>
       <c r="C4" t="n">
-        <v>61.3121076256218</v>
+        <v>68.20397650943441</v>
       </c>
       <c r="D4" t="n">
-        <v>28.49915410658066</v>
+        <v>35.31444666946201</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.2554596917492</v>
+        <v>29.69786805346602</v>
       </c>
       <c r="C5" t="n">
-        <v>63.59270754258716</v>
+        <v>93.87962421860125</v>
       </c>
       <c r="D5" t="n">
-        <v>30.16419821298325</v>
+        <v>32.79037332184348</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.86794708601219</v>
+        <v>12.84027822384404</v>
       </c>
       <c r="C6" t="n">
-        <v>30.95352336719769</v>
+        <v>46.65166915810419</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>37.99756314516856</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.2097595180061</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06636702051607</v>
+        <v>18.03773075784775</v>
       </c>
       <c r="C21" t="n">
-        <v>117.861537229081</v>
+        <v>117.6747197059591</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882425531625169</v>
+        <v>6.012576919282582</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.522330836388309</v>
+        <v>8.044440688598364</v>
       </c>
       <c r="C2" t="n">
-        <v>10.46641227497525</v>
+        <v>6.849653732529996</v>
       </c>
       <c r="D2" t="n">
-        <v>21.19200594387165</v>
+        <v>23.17022756792897</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.92747384307275</v>
+        <v>18.77592484372025</v>
       </c>
       <c r="C3" t="n">
-        <v>19.27170743436489</v>
+        <v>30.18383316706819</v>
       </c>
       <c r="D3" t="n">
-        <v>42.16115515887927</v>
+        <v>46.00960615952677</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.45413258090555</v>
+        <v>25.61477935150353</v>
       </c>
       <c r="C4" t="n">
-        <v>49.3406761200362</v>
+        <v>52.62069519992479</v>
       </c>
       <c r="D4" t="n">
-        <v>34.72736154232243</v>
+        <v>38.99011007416208</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.67208057124834</v>
+        <v>24.88730430265665</v>
       </c>
       <c r="C5" t="n">
-        <v>67.49515466696822</v>
+        <v>82.22137023067039</v>
       </c>
       <c r="D5" t="n">
-        <v>26.89988709636261</v>
+        <v>30.65507206510666</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.47801332097696</v>
+        <v>14.20883452356409</v>
       </c>
       <c r="C6" t="n">
-        <v>45.72588107299945</v>
+        <v>66.05296728942966</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43025184083414</v>
+        <v>30.5510068084565</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>28.26647990067416</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.061645812878435</v>
+        <v>7.044126132952935</v>
       </c>
       <c r="C21" t="n">
-        <v>66.20292949573533</v>
+        <v>66.03868249643376</v>
       </c>
       <c r="D21" t="n">
-        <v>5.296234359658826</v>
+        <v>4.402578833095585</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.715334223497431</v>
+        <v>6.741661485062847</v>
       </c>
       <c r="C2" t="n">
-        <v>9.279479300540853</v>
+        <v>4.009457624143973</v>
       </c>
       <c r="D2" t="n">
-        <v>23.56685364044468</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.68127615348505</v>
+        <v>24.40624792757571</v>
       </c>
       <c r="C3" t="n">
-        <v>33.45305302221006</v>
+        <v>27.9945357865978</v>
       </c>
       <c r="D3" t="n">
-        <v>50.21639507222435</v>
+        <v>54.35446164562466</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.4698816019025</v>
+        <v>32.53217367562655</v>
       </c>
       <c r="C4" t="n">
-        <v>48.77911643320702</v>
+        <v>66.91494177375834</v>
       </c>
       <c r="D4" t="n">
-        <v>49.48106604174349</v>
+        <v>54.05011985730815</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.93072218582176</v>
+        <v>32.93763547748049</v>
       </c>
       <c r="C5" t="n">
-        <v>82.39317607891357</v>
+        <v>91.42525495798422</v>
       </c>
       <c r="D5" t="n">
-        <v>34.11573272257667</v>
+        <v>37.92000507653306</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.37992066601029</v>
+        <v>25.03652995370216</v>
       </c>
       <c r="C6" t="n">
-        <v>82.55614619781855</v>
+        <v>103.5272589082347</v>
       </c>
       <c r="D6" t="n">
-        <v>32.32207966691774</v>
+        <v>33.89189424600839</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.83947640258903</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>47.78951474732623</v>
+        <v>66.35436383463342</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>24.53387512912779</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6213,7 +6213,7 @@
         <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.285720912365288</v>
+        <v>7.260804163727018</v>
       </c>
       <c r="C21" t="n">
-        <v>75.58935446578987</v>
+        <v>75.33084319866782</v>
       </c>
       <c r="D21" t="n">
-        <v>6.375005798319627</v>
+        <v>5.445603122795264</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.584180941755857</v>
+        <v>5.184609626127406</v>
       </c>
       <c r="C2" t="n">
-        <v>13.77392029058275</v>
+        <v>8.722828352232911</v>
       </c>
       <c r="D2" t="n">
-        <v>20.58724935805562</v>
+        <v>23.8859216443249</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.92042168269378</v>
+        <v>23.75338570425158</v>
       </c>
       <c r="C3" t="n">
-        <v>35.06311925717483</v>
+        <v>20.69524160552276</v>
       </c>
       <c r="D3" t="n">
-        <v>57.41751448287471</v>
+        <v>59.64608177151496</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.91130821591507</v>
+        <v>40.91728081759857</v>
       </c>
       <c r="C4" t="n">
-        <v>69.39090948386881</v>
+        <v>68.08911202803753</v>
       </c>
       <c r="D4" t="n">
-        <v>63.53282093262809</v>
+        <v>67.79556946446775</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.72932503773092</v>
+        <v>41.25794727097221</v>
       </c>
       <c r="C5" t="n">
-        <v>86.12381735505146</v>
+        <v>109.5385001013379</v>
       </c>
       <c r="D5" t="n">
-        <v>43.88412237983243</v>
+        <v>48.79286090106649</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.83276839957533</v>
+        <v>35.62271544859552</v>
       </c>
       <c r="C6" t="n">
-        <v>109.8467688804714</v>
+        <v>126.3901994447344</v>
       </c>
       <c r="D6" t="n">
-        <v>36.14598697495907</v>
+        <v>37.95731148929444</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="C7" t="n">
-        <v>87.43445054022094</v>
+        <v>110.9698882541297</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>45.89670517353839</v>
+        <v>60.0829594999048</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>27.62343515439249</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.496911100087268</v>
+        <v>7.463653518394874</v>
       </c>
       <c r="C21" t="n">
-        <v>85.27736376349267</v>
+        <v>83.96610208194232</v>
       </c>
       <c r="D21" t="n">
-        <v>7.496911100087268</v>
+        <v>6.530696828595514</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_54_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_54_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497635120521</v>
+        <v>10.84497633006114</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907200808023</v>
+        <v>37.78907193440421</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.200718500022854</v>
+        <v>2.029272504678157</v>
       </c>
       <c r="C2" t="n">
-        <v>11.32249627307846</v>
+        <v>3.412555019961913</v>
       </c>
       <c r="D2" t="n">
-        <v>22.93755336202248</v>
+        <v>15.0207398749762</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.45471341798229</v>
+        <v>15.9730351480956</v>
       </c>
       <c r="C3" t="n">
-        <v>27.82763867687584</v>
+        <v>36.29521262600458</v>
       </c>
       <c r="D3" t="n">
-        <v>64.14739499548659</v>
+        <v>84.89172398622169</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.3677230873986</v>
+        <v>27.41432289338793</v>
       </c>
       <c r="C4" t="n">
-        <v>59.39769960234052</v>
+        <v>83.80002053909925</v>
       </c>
       <c r="D4" t="n">
-        <v>80.81354402278045</v>
+        <v>98.48991143774427</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.63363784652926</v>
+        <v>29.25608158655496</v>
       </c>
       <c r="C5" t="n">
-        <v>117.7360934317988</v>
+        <v>80.724204981694</v>
       </c>
       <c r="D5" t="n">
-        <v>60.13204688511715</v>
+        <v>55.61600744558182</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.36361617013237</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="C6" t="n">
-        <v>148.890875078367</v>
+        <v>52.89067581859268</v>
       </c>
       <c r="D6" t="n">
-        <v>44.27682146153116</v>
+        <v>30.47050349670826</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.79978988825843</v>
+        <v>7.126506585127596</v>
       </c>
       <c r="C7" t="n">
-        <v>147.1414006693992</v>
+        <v>34.07548106670254</v>
       </c>
       <c r="D7" t="n">
-        <v>38.5669768136317</v>
+        <v>29.2845522699781</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.10557108816892</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>102.0575825949772</v>
+        <v>28.37250865273282</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>52.36249555370786</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.651435643572737</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.77365717831944</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.651435643572737</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.519786503903068</v>
+        <v>2.300234871050277</v>
       </c>
       <c r="C2" t="n">
-        <v>14.51513980728909</v>
+        <v>5.227806525114265</v>
       </c>
       <c r="D2" t="n">
-        <v>21.9145722541973</v>
+        <v>20.01587219418397</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.37617360164255</v>
+        <v>11.24101121362598</v>
       </c>
       <c r="C3" t="n">
-        <v>35.62762418711675</v>
+        <v>22.89926520155685</v>
       </c>
       <c r="D3" t="n">
-        <v>66.40541471525425</v>
+        <v>77.42553269542469</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.66202641449439</v>
+        <v>29.58398531977338</v>
       </c>
       <c r="C4" t="n">
-        <v>63.5583463729385</v>
+        <v>87.83304010814514</v>
       </c>
       <c r="D4" t="n">
-        <v>90.7812284639983</v>
+        <v>117.7871443124196</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.18680377237672</v>
+        <v>35.51472320112837</v>
       </c>
       <c r="C5" t="n">
-        <v>113.6863841517807</v>
+        <v>122.2766765639403</v>
       </c>
       <c r="D5" t="n">
-        <v>72.91931073293185</v>
+        <v>77.04265109076846</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.18502020341747</v>
+        <v>28.98119222936585</v>
       </c>
       <c r="C6" t="n">
-        <v>165.1122923956371</v>
+        <v>92.498305198726</v>
       </c>
       <c r="D6" t="n">
-        <v>51.07935130425731</v>
+        <v>39.92964262712628</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.50142070162541</v>
+        <v>14.25301317025519</v>
       </c>
       <c r="C7" t="n">
-        <v>179.1208503875348</v>
+        <v>55.81432048183967</v>
       </c>
       <c r="D7" t="n">
-        <v>42.16017341117502</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.11663235482289</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>143.3646172511617</v>
+        <v>37.21805546799658</v>
       </c>
       <c r="D8" t="n">
-        <v>37.46840113257952</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.6484365108884</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>85.75468021825461</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>44.84132639147307</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.823524144610053</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7278733618544</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.80146466268631</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.314020396638737</v>
+        <v>1.224239387195773</v>
       </c>
       <c r="C2" t="n">
-        <v>15.92394776288326</v>
+        <v>2.157881453934489</v>
       </c>
       <c r="D2" t="n">
-        <v>23.61692277336127</v>
+        <v>13.48430471782994</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.4988920646734</v>
+        <v>10.88267330157589</v>
       </c>
       <c r="C3" t="n">
-        <v>44.69897297435728</v>
+        <v>23.21342446691583</v>
       </c>
       <c r="D3" t="n">
-        <v>67.3331662957675</v>
+        <v>78.21583959734339</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.76038111136832</v>
+        <v>32.49388551516093</v>
       </c>
       <c r="C4" t="n">
-        <v>74.50876026610743</v>
+        <v>84.13185126313466</v>
       </c>
       <c r="D4" t="n">
-        <v>99.80447161373074</v>
+        <v>130.6009153482489</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.16855147662353</v>
+        <v>36.20194659410114</v>
       </c>
       <c r="C5" t="n">
-        <v>113.6618404591745</v>
+        <v>149.8637870532756</v>
       </c>
       <c r="D5" t="n">
-        <v>83.64490440182826</v>
+        <v>86.95830290366123</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.59761628110839</v>
+        <v>21.93715245139498</v>
       </c>
       <c r="C6" t="n">
-        <v>170.465762626895</v>
+        <v>121.7210073633366</v>
       </c>
       <c r="D6" t="n">
-        <v>59.08943082320704</v>
+        <v>40.37241084174159</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>51.08327829507428</v>
+        <v>4.611268966847268</v>
       </c>
       <c r="C7" t="n">
-        <v>205.1116391097649</v>
+        <v>56.65273302126644</v>
       </c>
       <c r="D7" t="n">
-        <v>46.35223610830891</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.46148784092078</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>181.4171582677681</v>
+        <v>38.55323234577224</v>
       </c>
       <c r="D8" t="n">
-        <v>39.38771789438203</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.75156107756332</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>122.8078020719377</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>67.76022654711485</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>39.98167525545134</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.979665933420957</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.7254901011829</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.974582416776197</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.803511590430396</v>
+        <v>0.953277020823653</v>
       </c>
       <c r="C2" t="n">
-        <v>11.08294983324224</v>
+        <v>3.75518496874405</v>
       </c>
       <c r="D2" t="n">
-        <v>19.53972455762426</v>
+        <v>14.76744896728052</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.44690049407733</v>
+        <v>7.441647598190823</v>
       </c>
       <c r="C3" t="n">
-        <v>63.29327449279187</v>
+        <v>14.85875150377547</v>
       </c>
       <c r="D3" t="n">
-        <v>73.19910882864218</v>
+        <v>71.81484456565418</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.93759441975148</v>
+        <v>27.2101193709046</v>
       </c>
       <c r="C4" t="n">
-        <v>96.79246965710152</v>
+        <v>70.62889333892403</v>
       </c>
       <c r="D4" t="n">
-        <v>95.20989235785567</v>
+        <v>139.2029887328595</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.80924751240241</v>
+        <v>42.68148144213009</v>
       </c>
       <c r="C5" t="n">
-        <v>101.8563243156066</v>
+        <v>154.1343895667493</v>
       </c>
       <c r="D5" t="n">
-        <v>57.7758523949248</v>
+        <v>111.1092964281328</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.71830482880595</v>
+        <v>33.73088762251191</v>
       </c>
       <c r="C6" t="n">
-        <v>135.0845571135441</v>
+        <v>181.2129547452848</v>
       </c>
       <c r="D6" t="n">
-        <v>30.51075515258238</v>
+        <v>55.90955000915161</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.4992929753009</v>
+        <v>12.51630148144259</v>
       </c>
       <c r="C7" t="n">
-        <v>127.5584792127881</v>
+        <v>112.5868267230242</v>
       </c>
       <c r="D7" t="n">
-        <v>27.66761380108361</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.59934912567606</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>90.45823346930109</v>
+        <v>55.49328898255096</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>51.69687061022852</v>
+        <v>36.16562192904399</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.62994753542373</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.363868545377072</v>
+        <v>0.5586144437164351</v>
       </c>
       <c r="C2" t="n">
-        <v>5.140430979436299</v>
+        <v>1.792671307954676</v>
       </c>
       <c r="D2" t="n">
-        <v>13.38122120888403</v>
+        <v>10.93176068678823</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.13764996723958</v>
+        <v>5.64504929941916</v>
       </c>
       <c r="C3" t="n">
-        <v>54.36918786118836</v>
+        <v>14.93238258159398</v>
       </c>
       <c r="D3" t="n">
-        <v>73.01748550335653</v>
+        <v>67.95166734944299</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.68005772606933</v>
+        <v>22.44962475301181</v>
       </c>
       <c r="C4" t="n">
-        <v>129.0693889296239</v>
+        <v>56.13044324260714</v>
       </c>
       <c r="D4" t="n">
-        <v>106.9133067401819</v>
+        <v>143.5933644662512</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.07985002587604</v>
+        <v>44.8167826988669</v>
       </c>
       <c r="C5" t="n">
-        <v>136.8065425867931</v>
+        <v>149.1029325824844</v>
       </c>
       <c r="D5" t="n">
-        <v>73.31200981463057</v>
+        <v>130.891512668706</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.39378830705677</v>
+        <v>41.53970886209105</v>
       </c>
       <c r="C6" t="n">
-        <v>154.0833386861284</v>
+        <v>216.5136569468874</v>
       </c>
       <c r="D6" t="n">
-        <v>36.58875518957439</v>
+        <v>70.15863618858982</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.12190094624263</v>
+        <v>14.07335334037803</v>
       </c>
       <c r="C7" t="n">
-        <v>156.1842787732166</v>
+        <v>166.424889076215</v>
       </c>
       <c r="D7" t="n">
-        <v>30.06307819944583</v>
+        <v>40.78278138211675</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>118.1631536831461</v>
+        <v>81.69613520889833</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>55.35780779936488</v>
+        <v>46.03905859065416</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.109595889977149</v>
+        <v>0.8501935118777378</v>
       </c>
       <c r="C2" t="n">
-        <v>8.61189086165302</v>
+        <v>5.810964661436871</v>
       </c>
       <c r="D2" t="n">
-        <v>17.99936240966102</v>
+        <v>11.31464229144449</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.00310947402876</v>
+        <v>3.774819922828986</v>
       </c>
       <c r="C3" t="n">
-        <v>36.37375244234433</v>
+        <v>10.67650628368406</v>
       </c>
       <c r="D3" t="n">
-        <v>67.27917017203391</v>
+        <v>61.57521601035995</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.64475586644545</v>
+        <v>16.78297700409922</v>
       </c>
       <c r="C4" t="n">
-        <v>133.5108155436365</v>
+        <v>47.01786105178824</v>
       </c>
       <c r="D4" t="n">
-        <v>117.1872964651248</v>
+        <v>144.6143820786679</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.90299657039137</v>
+        <v>40.84070449666732</v>
       </c>
       <c r="C5" t="n">
-        <v>184.224956701914</v>
+        <v>127.0136092369311</v>
       </c>
       <c r="D5" t="n">
-        <v>91.40071126537806</v>
+        <v>149.201107352909</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.08185457901354</v>
+        <v>50.15356321915257</v>
       </c>
       <c r="C6" t="n">
-        <v>182.984027603746</v>
+        <v>226.7778291947878</v>
       </c>
       <c r="D6" t="n">
-        <v>48.1409804254466</v>
+        <v>90.00270253453061</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.2845522699781</v>
+        <v>28.02693346083794</v>
       </c>
       <c r="C7" t="n">
-        <v>188.4032749311884</v>
+        <v>235.1148306992516</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>49.0471335564664</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.01935721664445</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>158.2184600164159</v>
+        <v>142.7804773671348</v>
       </c>
       <c r="D8" t="n">
-        <v>29.04009709162065</v>
+        <v>41.8911745402114</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>92.74374212478766</v>
+        <v>69.66874408417063</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>46.40721397974673</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.516219365984575</v>
+        <v>0.5703954161673969</v>
       </c>
       <c r="C2" t="n">
-        <v>4.191080949429634</v>
+        <v>3.020837685967436</v>
       </c>
       <c r="D2" t="n">
-        <v>12.55262614649972</v>
+        <v>8.14752419754428</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.43369580556561</v>
+        <v>5.517422097867074</v>
       </c>
       <c r="C3" t="n">
-        <v>37.52239725631309</v>
+        <v>16.64062358698343</v>
       </c>
       <c r="D3" t="n">
-        <v>68.13329067472864</v>
+        <v>65.71328258376025</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.7543517564226</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="C4" t="n">
-        <v>131.5836448002</v>
+        <v>66.14917856444583</v>
       </c>
       <c r="D4" t="n">
-        <v>124.6917759163874</v>
+        <v>150.5490469508399</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.27744335633691</v>
+        <v>31.26866438026092</v>
       </c>
       <c r="C5" t="n">
-        <v>226.7100886031947</v>
+        <v>190.5081420090936</v>
       </c>
       <c r="D5" t="n">
-        <v>96.50579932746149</v>
+        <v>136.0947755012141</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.06548366321083</v>
+        <v>17.38871533761951</v>
       </c>
       <c r="C6" t="n">
-        <v>220.5388225342993</v>
+        <v>212.6494979829719</v>
       </c>
       <c r="D6" t="n">
-        <v>47.41645061971246</v>
+        <v>73.29826534677112</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.282424543653592</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>199.7218442134499</v>
+        <v>100.3699582913769</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>114.8252114887069</v>
+        <v>51.32086123950201</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>35.38905949498476</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.157300616857742</v>
+        <v>0.3396847056693963</v>
       </c>
       <c r="C2" t="n">
-        <v>10.54200684820225</v>
+        <v>1.764200624531518</v>
       </c>
       <c r="D2" t="n">
-        <v>15.84638969424777</v>
+        <v>6.21446296788231</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.28933783531232</v>
+        <v>3.735550014659113</v>
       </c>
       <c r="C3" t="n">
-        <v>26.94406574305371</v>
+        <v>13.98990478551705</v>
       </c>
       <c r="D3" t="n">
-        <v>62.97420648891165</v>
+        <v>57.402788267311</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.07868835172254</v>
+        <v>18.13582534055133</v>
       </c>
       <c r="C4" t="n">
-        <v>114.4305489115997</v>
+        <v>51.07640606114455</v>
       </c>
       <c r="D4" t="n">
-        <v>128.954524448227</v>
+        <v>143.3891609437679</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.69592992025331</v>
+        <v>29.10881943091793</v>
       </c>
       <c r="C5" t="n">
-        <v>235.545817941416</v>
+        <v>142.3288734231814</v>
       </c>
       <c r="D5" t="n">
-        <v>114.2018016965102</v>
+        <v>141.3225820263284</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.57116584635595</v>
+        <v>17.75098024048658</v>
       </c>
       <c r="C6" t="n">
-        <v>281.7213394629605</v>
+        <v>211.8444648654896</v>
       </c>
       <c r="D6" t="n">
-        <v>62.14855666964009</v>
+        <v>81.06683493047613</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.70269467652924</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>252.6017208072958</v>
+        <v>137.8589761257456</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>173.0723027816702</v>
+        <v>56.41122308602172</v>
       </c>
       <c r="D8" t="n">
-        <v>32.54493639578176</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>71.66561891460864</v>
+        <v>28.95468504135117</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>21.52187317249857</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>18.64829764216817</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.411172361630166</v>
+        <v>0.5271985171805372</v>
       </c>
       <c r="C2" t="n">
-        <v>6.406885517914684</v>
+        <v>3.848451000647497</v>
       </c>
       <c r="D2" t="n">
-        <v>11.21254053020282</v>
+        <v>7.865762606425444</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.92961726493049</v>
+        <v>2.316924582022473</v>
       </c>
       <c r="C3" t="n">
-        <v>33.64940256305943</v>
+        <v>9.665306148309849</v>
       </c>
       <c r="D3" t="n">
-        <v>61.4672237628928</v>
+        <v>49.05302404269188</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.17780381212246</v>
+        <v>12.30326222962103</v>
       </c>
       <c r="C4" t="n">
-        <v>97.2008767020682</v>
+        <v>42.168027392809</v>
       </c>
       <c r="D4" t="n">
-        <v>130.6009153482489</v>
+        <v>140.1474300243449</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.08925089675779</v>
+        <v>28.98610096788708</v>
       </c>
       <c r="C5" t="n">
-        <v>234.3186333111075</v>
+        <v>115.6498795602743</v>
       </c>
       <c r="D5" t="n">
-        <v>127.0381529295373</v>
+        <v>161.5220410412065</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.69570893607505</v>
+        <v>28.77993394999525</v>
       </c>
       <c r="C6" t="n">
-        <v>323.8245715072892</v>
+        <v>222.7124119515017</v>
       </c>
       <c r="D6" t="n">
-        <v>72.2114706381699</v>
+        <v>105.9826099165559</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.36711688812607</v>
+        <v>12.69596131131975</v>
       </c>
       <c r="C7" t="n">
-        <v>307.3380823098724</v>
+        <v>226.3713856452295</v>
       </c>
       <c r="D7" t="n">
-        <v>41.32176087174825</v>
+        <v>49.76577287597506</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>3.00414797499524</v>
       </c>
       <c r="C8" t="n">
-        <v>215.9648599802133</v>
+        <v>122.0852357616121</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>78.32186834940201</v>
+        <v>50.25468323268996</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>23.62968549351647</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.642283982755667</v>
+        <v>1.148644813968768</v>
       </c>
       <c r="C2" t="n">
-        <v>5.716716881829178</v>
+        <v>6.126105674500097</v>
       </c>
       <c r="D2" t="n">
-        <v>13.76999329976576</v>
+        <v>15.09142570968197</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.64214511403542</v>
+        <v>2.032217747790897</v>
       </c>
       <c r="C3" t="n">
-        <v>29.49660977409542</v>
+        <v>12.57618809140164</v>
       </c>
       <c r="D3" t="n">
-        <v>57.02481540117598</v>
+        <v>44.27682146153115</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.26866438026091</v>
+        <v>8.283005380730339</v>
       </c>
       <c r="C4" t="n">
-        <v>91.25344910974103</v>
+        <v>32.45559735469531</v>
       </c>
       <c r="D4" t="n">
-        <v>130.5498644676281</v>
+        <v>132.3621707296677</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.56754195517523</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="C5" t="n">
-        <v>211.2230185687013</v>
+        <v>94.86137192284806</v>
       </c>
       <c r="D5" t="n">
-        <v>137.4446785945535</v>
+        <v>175.2665089006618</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.03409309887072</v>
+        <v>34.37491411649783</v>
       </c>
       <c r="C6" t="n">
-        <v>343.2661212944888</v>
+        <v>204.1563985935327</v>
       </c>
       <c r="D6" t="n">
-        <v>88.27188133194348</v>
+        <v>130.4556166880204</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.09922293805371</v>
+        <v>23.05634483423634</v>
       </c>
       <c r="C7" t="n">
-        <v>368.7218575179043</v>
+        <v>276.6761380108361</v>
       </c>
       <c r="D7" t="n">
-        <v>48.62792728675301</v>
+        <v>65.63572451512475</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>288.648551264126</v>
+        <v>211.0413952434156</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>141.6671754705189</v>
+        <v>99.62186654074081</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>25.84843530511426</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>51.95899724726245</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>21.49536598448391</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.032258805519903</v>
+        <v>9.465029616643498</v>
       </c>
       <c r="C2" t="n">
-        <v>11.75642875835555</v>
+        <v>6.826091787628073</v>
       </c>
       <c r="D2" t="n">
-        <v>9.52295273119406</v>
+        <v>14.35020619297563</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.661518026213103</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C2" t="n">
-        <v>3.384084336538756</v>
+        <v>8.63348931114645</v>
       </c>
       <c r="D2" t="n">
-        <v>10.24453729381547</v>
+        <v>13.98303255158732</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.3727863901733</v>
+        <v>2.901064466049325</v>
       </c>
       <c r="C3" t="n">
-        <v>32.32895190084746</v>
+        <v>18.28505099159684</v>
       </c>
       <c r="D3" t="n">
-        <v>62.45388020566084</v>
+        <v>45.5383672614883</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.58018150214342</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C4" t="n">
-        <v>129.5160841350562</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D4" t="n">
-        <v>132.4515097707542</v>
+        <v>125.5213527264759</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.05468443846411</v>
+        <v>19.29134238844983</v>
       </c>
       <c r="C5" t="n">
-        <v>299.9975547252191</v>
+        <v>77.92622402459058</v>
       </c>
       <c r="D5" t="n">
-        <v>125.8600556844411</v>
+        <v>180.4206843479576</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.92456965768902</v>
+        <v>33.93214590188251</v>
       </c>
       <c r="C6" t="n">
-        <v>303.4169819791107</v>
+        <v>178.7173520810894</v>
       </c>
       <c r="D6" t="n">
-        <v>70.56115274733101</v>
+        <v>152.7952856981566</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>31.32069700858599</v>
       </c>
       <c r="C7" t="n">
-        <v>202.9557211512388</v>
+        <v>288.47380017277</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>83.18250123312798</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="C8" t="n">
-        <v>104.3941421310846</v>
+        <v>284.476123521077</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>43.89393985687489</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>39.60468413702056</v>
+        <v>171.2874854553494</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>75.73201790559897</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>22.49183990429443</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.72429312602266</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>12.80100831567416</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.336600593836414</v>
+        <v>7.867726101833938</v>
       </c>
       <c r="C2" t="n">
-        <v>10.54789733442773</v>
+        <v>5.635231822376692</v>
       </c>
       <c r="D2" t="n">
-        <v>14.54851922923348</v>
+        <v>22.09717732718721</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.93238258159398</v>
+        <v>15.2367243699105</v>
       </c>
       <c r="C3" t="n">
-        <v>29.6242369756475</v>
+        <v>13.47448724078747</v>
       </c>
       <c r="D3" t="n">
-        <v>11.13301896615883</v>
+        <v>12.79217258633594</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39714255714293</v>
+        <v>11.6772513684357</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13798162268945</v>
+        <v>59.94322369130325</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576134418487403</v>
+        <v>0.7784834245623797</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.250386722311942</v>
+        <v>3.820962064928586</v>
       </c>
       <c r="C2" t="n">
-        <v>4.73104218676538</v>
+        <v>3.482259106963436</v>
       </c>
       <c r="D2" t="n">
-        <v>18.1456428175938</v>
+        <v>27.81389420901639</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.19593293468864</v>
+        <v>22.96307880233289</v>
       </c>
       <c r="C3" t="n">
-        <v>36.82535638629786</v>
+        <v>19.17844140246144</v>
       </c>
       <c r="D3" t="n">
-        <v>20.66088043587412</v>
+        <v>29.02046213753572</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.30624853046277</v>
+        <v>18.59528326613884</v>
       </c>
       <c r="C4" t="n">
-        <v>45.69053815564656</v>
+        <v>22.47515019332223</v>
       </c>
       <c r="D4" t="n">
-        <v>20.90533561423158</v>
+        <v>21.02020009562846</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43652664345976</v>
+        <v>13.62625908203398</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11956969509131</v>
+        <v>73.74210797336036</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249795082833634</v>
+        <v>1.603089303768704</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.42317431825938</v>
+        <v>3.675663404700058</v>
       </c>
       <c r="C2" t="n">
-        <v>5.811946409141117</v>
+        <v>5.465389469541994</v>
       </c>
       <c r="D2" t="n">
-        <v>18.61197297711103</v>
+        <v>32.64114767079795</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.46805697521425</v>
+        <v>17.33766445699867</v>
       </c>
       <c r="C3" t="n">
-        <v>25.81996462169111</v>
+        <v>15.62942345160922</v>
       </c>
       <c r="D3" t="n">
-        <v>30.38018270791754</v>
+        <v>45.37147015176635</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.3497485290859</v>
+        <v>34.37000537797658</v>
       </c>
       <c r="C4" t="n">
-        <v>72.60711496298136</v>
+        <v>38.30092318578082</v>
       </c>
       <c r="D4" t="n">
-        <v>26.55922064298896</v>
+        <v>31.34524070119216</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.87347771933918</v>
+        <v>16.39518666092174</v>
       </c>
       <c r="C5" t="n">
-        <v>49.60280275707011</v>
+        <v>26.94897448157495</v>
       </c>
       <c r="D5" t="n">
-        <v>30.4587225242573</v>
+        <v>27.51347941151687</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72298322698279</v>
+        <v>14.83345701387539</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0101976845951</v>
+        <v>87.35258019282175</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180745806745699</v>
+        <v>2.472242835645898</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.723990026386404</v>
+        <v>2.634029090494193</v>
       </c>
       <c r="C2" t="n">
-        <v>9.830239762623313</v>
+        <v>3.757148464152543</v>
       </c>
       <c r="D2" t="n">
-        <v>26.72513600500667</v>
+        <v>31.07722357793278</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.93300447639974</v>
+        <v>14.73603304074462</v>
       </c>
       <c r="C3" t="n">
-        <v>23.93991776805847</v>
+        <v>19.04590546238812</v>
       </c>
       <c r="D3" t="n">
-        <v>37.76783418237479</v>
+        <v>60.95671495668446</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.30619177720055</v>
+        <v>34.33171721751096</v>
       </c>
       <c r="C4" t="n">
-        <v>68.20397650943441</v>
+        <v>38.82419471214436</v>
       </c>
       <c r="D4" t="n">
-        <v>35.31444666946201</v>
+        <v>47.01786105178824</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.69786805346602</v>
+        <v>34.63115026730624</v>
       </c>
       <c r="C5" t="n">
-        <v>93.87962421860125</v>
+        <v>51.93445355465628</v>
       </c>
       <c r="D5" t="n">
-        <v>32.79037332184348</v>
+        <v>32.37313054753858</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.84027822384404</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="C6" t="n">
-        <v>46.65166915810419</v>
+        <v>28.17615911188346</v>
       </c>
       <c r="D6" t="n">
-        <v>37.99756314516856</v>
+        <v>33.89189424600839</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03773075784775</v>
+        <v>16.07139344710152</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6747197059591</v>
+        <v>100.6576747476359</v>
       </c>
       <c r="D21" t="n">
-        <v>6.012576919282582</v>
+        <v>3.383451252021374</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.044440688598364</v>
+        <v>3.594178345247573</v>
       </c>
       <c r="C2" t="n">
-        <v>6.849653732529996</v>
+        <v>7.096072406295946</v>
       </c>
       <c r="D2" t="n">
-        <v>23.17022756792897</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.77592484372025</v>
+        <v>11.72697632722815</v>
       </c>
       <c r="C3" t="n">
-        <v>30.18383316706819</v>
+        <v>16.45900026169778</v>
       </c>
       <c r="D3" t="n">
-        <v>46.00960615952677</v>
+        <v>71.01472018669303</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.61477935150353</v>
+        <v>31.1027490182432</v>
       </c>
       <c r="C4" t="n">
-        <v>52.62069519992479</v>
+        <v>43.76336741221007</v>
       </c>
       <c r="D4" t="n">
-        <v>38.99011007416208</v>
+        <v>65.91944960165209</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.88730430265665</v>
+        <v>43.54051068334605</v>
       </c>
       <c r="C5" t="n">
-        <v>82.22137023067039</v>
+        <v>62.63550353094652</v>
       </c>
       <c r="D5" t="n">
-        <v>30.65507206510666</v>
+        <v>41.08614142272902</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.20883452356409</v>
+        <v>29.90698031447059</v>
       </c>
       <c r="C6" t="n">
-        <v>66.05296728942966</v>
+        <v>56.31206656789281</v>
       </c>
       <c r="D6" t="n">
-        <v>30.5510068084565</v>
+        <v>36.70951015719674</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.988660995905543</v>
+        <v>11.43834250217959</v>
       </c>
       <c r="C7" t="n">
-        <v>28.26647990067416</v>
+        <v>29.34443887993716</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.37874329632356</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.044126132952935</v>
+        <v>17.33551134849665</v>
       </c>
       <c r="C21" t="n">
-        <v>66.03868249643376</v>
+        <v>114.4143749000779</v>
       </c>
       <c r="D21" t="n">
-        <v>4.402578833095585</v>
+        <v>4.333877837124163</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.741661485062847</v>
+        <v>4.487568756112171</v>
       </c>
       <c r="C2" t="n">
-        <v>4.009457624143973</v>
+        <v>13.42539985557513</v>
       </c>
       <c r="D2" t="n">
-        <v>22.8688310227252</v>
+        <v>27.24055354973625</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.40624792757571</v>
+        <v>11.91841712955628</v>
       </c>
       <c r="C3" t="n">
-        <v>27.9945357865978</v>
+        <v>22.46729621168826</v>
       </c>
       <c r="D3" t="n">
-        <v>54.35446164562466</v>
+        <v>78.43182409227768</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.53217367562655</v>
+        <v>26.78894960578271</v>
       </c>
       <c r="C4" t="n">
-        <v>66.91494177375834</v>
+        <v>42.35946819513713</v>
       </c>
       <c r="D4" t="n">
-        <v>54.05011985730815</v>
+        <v>84.42539382670446</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.93763547748049</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="C5" t="n">
-        <v>91.42525495798422</v>
+        <v>71.86393195086653</v>
       </c>
       <c r="D5" t="n">
-        <v>37.92000507653306</v>
+        <v>53.4070751110265</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.03652995370216</v>
+        <v>43.87430490278997</v>
       </c>
       <c r="C6" t="n">
-        <v>103.5272589082347</v>
+        <v>77.56494086942776</v>
       </c>
       <c r="D6" t="n">
-        <v>33.89189424600839</v>
+        <v>41.17744395922398</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.21686843164731</v>
+        <v>22.57725195456389</v>
       </c>
       <c r="C7" t="n">
-        <v>66.35436383463342</v>
+        <v>54.07760879302705</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>32.21114217633784</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>38.63668090063322</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.260804163727018</v>
+        <v>17.73307717217758</v>
       </c>
       <c r="C21" t="n">
-        <v>75.33084319866782</v>
+        <v>127.6781556396786</v>
       </c>
       <c r="D21" t="n">
-        <v>5.445603122795264</v>
+        <v>5.319923151653275</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.184609626127406</v>
+        <v>3.975096454495335</v>
       </c>
       <c r="C2" t="n">
-        <v>8.722828352232911</v>
+        <v>8.269260912870884</v>
       </c>
       <c r="D2" t="n">
-        <v>23.8859216443249</v>
+        <v>21.43940636534184</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.75338570425158</v>
+        <v>16.99896149903352</v>
       </c>
       <c r="C3" t="n">
-        <v>20.69524160552276</v>
+        <v>39.39262663290327</v>
       </c>
       <c r="D3" t="n">
-        <v>59.64608177151496</v>
+        <v>86.09436492392405</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.91728081759857</v>
+        <v>21.6838615436993</v>
       </c>
       <c r="C4" t="n">
-        <v>68.08911202803753</v>
+        <v>62.29483707757286</v>
       </c>
       <c r="D4" t="n">
-        <v>67.79556946446775</v>
+        <v>75.93818492349079</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.25794727097221</v>
+        <v>24.71549845441346</v>
       </c>
       <c r="C5" t="n">
-        <v>109.5385001013379</v>
+        <v>46.33849164044945</v>
       </c>
       <c r="D5" t="n">
-        <v>48.79286090106649</v>
+        <v>40.49709280018094</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.62271544859552</v>
+        <v>14.00757624419349</v>
       </c>
       <c r="C6" t="n">
-        <v>126.3901994447344</v>
+        <v>35.58246379272141</v>
       </c>
       <c r="D6" t="n">
-        <v>37.95731148929444</v>
+        <v>25.76105975943631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.31963314542373</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="C7" t="n">
-        <v>110.9698882541297</v>
+        <v>22.63713856452295</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>27.12863431145211</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>60.0829594999048</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.463653518394874</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>83.96610208194232</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.530696828595514</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
